--- a/GunfireDungeon_Godot/excel/RoleBase@角色属性.xlsx
+++ b/GunfireDungeon_Godot/excel/RoleBase@角色属性.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24765" windowHeight="14685"/>
+    <workbookView windowWidth="24765" windowHeight="12495"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="70">
   <si>
     <t>Id</t>
   </si>
@@ -104,6 +104,9 @@
   </si>
   <si>
     <t>AsPoisoningResist</t>
+  </si>
+  <si>
+    <t>AsBleedingResist</t>
   </si>
   <si>
     <t>表Id</t>
@@ -186,6 +189,9 @@
   </si>
   <si>
     <t>中毒异常状态抗性</t>
+  </si>
+  <si>
+    <t>出血异常状态抗性</t>
   </si>
   <si>
     <t>string</t>
@@ -887,7 +893,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -905,9 +911,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1223,7 +1226,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Y13"/>
+  <dimension ref="A1:Z13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="13.75" style="3" customWidth="1"/>
@@ -1245,10 +1248,10 @@
     <col min="22" max="22" width="15.5" style="5" customWidth="1"/>
     <col min="23" max="23" width="16.125" style="5" customWidth="1"/>
     <col min="24" max="24" width="21.5" style="6" customWidth="1"/>
-    <col min="25" max="25" width="27" style="6" customWidth="1"/>
+    <col min="25" max="26" width="27" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23" customHeight="1" spans="1:25">
+    <row r="1" ht="23" customHeight="1" spans="1:26">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1318,176 +1321,185 @@
       <c r="W1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="7" t="s">
+      <c r="X1" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="7" t="s">
+      <c r="Y1" s="6" t="s">
         <v>24</v>
       </c>
+      <c r="Z1" s="6" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="2" ht="129" customHeight="1" spans="1:25">
+    <row r="2" ht="129" customHeight="1" spans="1:26">
       <c r="A2" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P2" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R2" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="S2" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="T2" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="U2" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="V2" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="W2" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="S2" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="T2" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="U2" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="V2" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="W2" s="5" t="s">
-        <v>41</v>
-      </c>
       <c r="X2" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Y2" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="Z2" s="6" t="s">
+        <v>50</v>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1" spans="1:25">
+    <row r="3" ht="30" customHeight="1" spans="1:26">
       <c r="A3" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="J3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="K3" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="K3" s="4" t="s">
-        <v>51</v>
-      </c>
       <c r="L3" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="N3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="O3" t="s">
+        <v>57</v>
+      </c>
+      <c r="P3" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="O3" t="s">
-        <v>55</v>
-      </c>
-      <c r="P3" s="5" t="s">
-        <v>52</v>
-      </c>
       <c r="Q3" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="T3" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="U3" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="V3" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="W3" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="X3" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="Y3" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
+      </c>
+      <c r="Z3" s="6" t="s">
+        <v>53</v>
       </c>
     </row>
-    <row r="4" ht="69" customHeight="1" spans="1:25">
+    <row r="4" ht="69" customHeight="1" spans="1:26">
       <c r="A4" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D4" s="4">
         <v>80</v>
@@ -1508,7 +1520,7 @@
         <v>27</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K4" s="4">
         <v>2</v>
@@ -1551,19 +1563,22 @@
       </c>
       <c r="Y4" s="6">
         <v>30</v>
+      </c>
+      <c r="Z4" s="6">
+        <v>40</v>
       </c>
     </row>
     <row r="5" ht="69" customHeight="1"/>
     <row r="6" ht="69" customHeight="1"/>
     <row r="7" ht="69" customHeight="1" spans="1:23">
       <c r="A7" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D7" s="4">
         <v>1000</v>
@@ -1603,15 +1618,15 @@
       </c>
     </row>
     <row r="8" ht="69" customHeight="1"/>
-    <row r="9" ht="30" customHeight="1" spans="1:25">
+    <row r="9" ht="30" customHeight="1" spans="1:26">
       <c r="A9" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D9" s="4">
         <v>60</v>
@@ -1644,7 +1659,7 @@
         <v>3</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="P9" s="5">
         <v>1</v>
@@ -1674,15 +1689,18 @@
         <v>30</v>
       </c>
       <c r="Y9" s="6">
+        <v>30</v>
+      </c>
+      <c r="Z9" s="6">
         <v>30</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="2:23">
       <c r="B10" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D10" s="4">
         <v>50</v>
@@ -1715,7 +1733,7 @@
         <v>3</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="P10" s="5">
         <v>1</v>
@@ -1763,17 +1781,17 @@
   <sheetData>
     <row r="2" ht="23.25" spans="2:2">
       <c r="B2" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" ht="15" spans="2:2">
       <c r="B3" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" ht="15" spans="2:2">
       <c r="B4" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/GunfireDungeon_Godot/excel/RoleBase@角色属性.xlsx
+++ b/GunfireDungeon_Godot/excel/RoleBase@角色属性.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24765" windowHeight="12495"/>
+    <workbookView windowWidth="24570" windowHeight="12240"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="71">
   <si>
     <t>Id</t>
   </si>
@@ -183,6 +183,9 @@
   </si>
   <si>
     <t>暗影属性伤害抗性</t>
+  </si>
+  <si>
+    <t>真实伤害属性伤害抗性，真实伤害指的是异常状态下受到的各种伤害，比如烧伤、中毒、出血等</t>
   </si>
   <si>
     <t>燃烧异常状态抗性</t>
@@ -1399,107 +1402,107 @@
         <v>47</v>
       </c>
       <c r="W2" s="5" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="X2" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Y2" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Z2" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:26">
       <c r="A3" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>51</v>
-      </c>
       <c r="D3" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="I3" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="J3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="K3" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="L3" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="I3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="J3" s="4" t="s">
+      <c r="M3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="O3" t="s">
+        <v>58</v>
+      </c>
+      <c r="P3" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="K3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="O3" t="s">
-        <v>57</v>
-      </c>
-      <c r="P3" s="5" t="s">
+      <c r="Q3" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="R3" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="S3" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="T3" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="U3" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="V3" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="W3" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="X3" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="Q3" s="5" t="s">
+      <c r="Y3" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="R3" s="5" t="s">
+      <c r="Z3" s="6" t="s">
         <v>54</v>
-      </c>
-      <c r="S3" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="T3" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="U3" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="V3" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="W3" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="X3" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y3" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z3" s="6" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="4" ht="69" customHeight="1" spans="1:26">
       <c r="A4" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D4" s="4">
         <v>80</v>
@@ -1520,7 +1523,7 @@
         <v>27</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K4" s="4">
         <v>2</v>
@@ -1572,13 +1575,13 @@
     <row r="6" ht="69" customHeight="1"/>
     <row r="7" ht="69" customHeight="1" spans="1:23">
       <c r="A7" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D7" s="4">
         <v>1000</v>
@@ -1620,13 +1623,13 @@
     <row r="8" ht="69" customHeight="1"/>
     <row r="9" ht="30" customHeight="1" spans="1:26">
       <c r="A9" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D9" s="4">
         <v>60</v>
@@ -1659,7 +1662,7 @@
         <v>3</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P9" s="5">
         <v>1</v>
@@ -1697,10 +1700,10 @@
     </row>
     <row r="10" ht="34" customHeight="1" spans="2:23">
       <c r="B10" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D10" s="4">
         <v>50</v>
@@ -1733,7 +1736,7 @@
         <v>3</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="P10" s="5">
         <v>1</v>
@@ -1781,17 +1784,17 @@
   <sheetData>
     <row r="2" ht="23.25" spans="2:2">
       <c r="B2" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" ht="15" spans="2:2">
       <c r="B3" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" ht="15" spans="2:2">
       <c r="B4" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/GunfireDungeon_Godot/excel/RoleBase@角色属性.xlsx
+++ b/GunfireDungeon_Godot/excel/RoleBase@角色属性.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24570" windowHeight="12240"/>
+    <workbookView windowHeight="18800"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="81">
   <si>
     <t>Id</t>
   </si>
@@ -40,9 +40,15 @@
     <t>Remark</t>
   </si>
   <si>
+    <t>LiftType</t>
+  </si>
+  <si>
     <t>Hp</t>
   </si>
   <si>
+    <t>Armor</t>
+  </si>
+  <si>
     <t>Shield</t>
   </si>
   <si>
@@ -73,6 +79,9 @@
     <t>Camp</t>
   </si>
   <si>
+    <t>RoleStrength</t>
+  </si>
+  <si>
     <t>AiAttr</t>
   </si>
   <si>
@@ -118,11 +127,20 @@
     <t>备注</t>
   </si>
   <si>
+    <t xml:space="preserve">判断角色以生命值、护盾值、装甲值的其中一种作为存活判定。
+Hp（生命值）：0
+Shield（护甲值）：1
+Armor（装甲值）：2
+</t>
+  </si>
+  <si>
     <t>血量</t>
   </si>
   <si>
-    <t>护盾值
-敌人可以不用填写</t>
+    <t>装甲值</t>
+  </si>
+  <si>
+    <t>护盾值</t>
   </si>
   <si>
     <t>移动速度</t>
@@ -158,6 +176,14 @@
 Camp1~5（阵营1, 玩家，其他都是敌人）：2~6</t>
   </si>
   <si>
+    <t xml:space="preserve">角色强度，作为非玩家角色，标识该敌人或NPC是 普通、稀有、精英等，不同类型的敌人生命血条会有特殊表现。其强度也不相同。
+Normal（普通）：0
+Rare（稀有）：1
+Elite（精英）：2
+Boss（头目）：3
+</t>
+  </si>
+  <si>
     <t>绑定的Ai属性</t>
   </si>
   <si>
@@ -203,6 +229,9 @@
     <t>$ActivityBase</t>
   </si>
   <si>
+    <t>LifeTypeEnum</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -213,6 +242,9 @@
   </si>
   <si>
     <t>CampEnum</t>
+  </si>
+  <si>
+    <t>RoleStrengthEnum</t>
   </si>
   <si>
     <t>$AiRoleAttr</t>
@@ -235,10 +267,16 @@
     <t>商店老板</t>
   </si>
   <si>
+    <t>Elite</t>
+  </si>
+  <si>
     <t>enemy0001</t>
   </si>
   <si>
     <t>敌人1</t>
+  </si>
+  <si>
+    <t>Normal</t>
   </si>
   <si>
     <t>enemy0002</t>
@@ -1229,32 +1267,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:AC13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="13.75" style="3" customWidth="1"/>
     <col min="2" max="2" width="17" style="4" customWidth="1"/>
-    <col min="3" max="5" width="14" style="4" customWidth="1"/>
-    <col min="6" max="6" width="18.125" style="4" customWidth="1"/>
-    <col min="7" max="7" width="17" style="4" customWidth="1"/>
-    <col min="8" max="9" width="15" style="4" customWidth="1"/>
-    <col min="10" max="10" width="29.375" style="4" customWidth="1"/>
-    <col min="11" max="13" width="20.125" style="4" customWidth="1"/>
-    <col min="14" max="14" width="28.75" style="4" customWidth="1"/>
-    <col min="15" max="15" width="16.25" customWidth="1"/>
-    <col min="16" max="16" width="23.55" style="5" customWidth="1"/>
-    <col min="17" max="17" width="20.5083333333333" style="5" customWidth="1"/>
-    <col min="18" max="18" width="23.2333333333333" style="5" customWidth="1"/>
-    <col min="19" max="19" width="17.75" style="5" customWidth="1"/>
-    <col min="20" max="20" width="19.5" style="5" customWidth="1"/>
-    <col min="21" max="21" width="16.5" style="5" customWidth="1"/>
-    <col min="22" max="22" width="15.5" style="5" customWidth="1"/>
-    <col min="23" max="23" width="16.125" style="5" customWidth="1"/>
-    <col min="24" max="24" width="21.5" style="6" customWidth="1"/>
-    <col min="25" max="26" width="27" style="6" customWidth="1"/>
+    <col min="3" max="3" width="14" style="4" customWidth="1"/>
+    <col min="4" max="4" width="23.0769230769231" style="4" customWidth="1"/>
+    <col min="5" max="7" width="14" style="4" customWidth="1"/>
+    <col min="8" max="8" width="18.125" style="4" customWidth="1"/>
+    <col min="9" max="9" width="17" style="4" customWidth="1"/>
+    <col min="10" max="11" width="15" style="4" customWidth="1"/>
+    <col min="12" max="12" width="29.375" style="4" customWidth="1"/>
+    <col min="13" max="15" width="20.125" style="4" customWidth="1"/>
+    <col min="16" max="16" width="28.75" style="4" customWidth="1"/>
+    <col min="17" max="17" width="44.375" style="4" customWidth="1"/>
+    <col min="18" max="18" width="16.25" customWidth="1"/>
+    <col min="19" max="19" width="23.5480769230769" style="5" customWidth="1"/>
+    <col min="20" max="20" width="20.5096153846154" style="5" customWidth="1"/>
+    <col min="21" max="21" width="23.2307692307692" style="5" customWidth="1"/>
+    <col min="22" max="22" width="17.75" style="5" customWidth="1"/>
+    <col min="23" max="23" width="19.5" style="5" customWidth="1"/>
+    <col min="24" max="24" width="16.5" style="5" customWidth="1"/>
+    <col min="25" max="25" width="15.5" style="5" customWidth="1"/>
+    <col min="26" max="26" width="16.125" style="5" customWidth="1"/>
+    <col min="27" max="27" width="21.5" style="6" customWidth="1"/>
+    <col min="28" max="29" width="27" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23" customHeight="1" spans="1:26">
+    <row r="1" ht="23" customHeight="1" spans="1:29">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1297,16 +1338,16 @@
       <c r="N1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="P1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="Q1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
       <c r="S1" s="5" t="s">
@@ -1324,285 +1365,318 @@
       <c r="W1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="6" t="s">
+      <c r="X1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="6" t="s">
+      <c r="Y1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="6" t="s">
+      <c r="Z1" s="5" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="6" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="2" ht="129" customHeight="1" spans="1:26">
+    <row r="2" ht="136" customHeight="1" spans="1:29">
       <c r="A2" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="R2" t="s">
+        <v>46</v>
+      </c>
+      <c r="S2" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="T2" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="U2" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="V2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="W2" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="X2" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y2" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z2" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA2" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB2" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC2" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:29">
+      <c r="A3" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="R3" t="s">
+        <v>66</v>
+      </c>
+      <c r="S3" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="T3" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="U3" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="V3" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="W3" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="X3" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y3" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z3" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="AA3" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB3" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC3" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" ht="69" customHeight="1" spans="1:29">
+      <c r="A4" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="4">
+        <v>80</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4">
+        <v>30</v>
+      </c>
+      <c r="H4" s="4">
+        <v>120</v>
+      </c>
+      <c r="I4" s="4">
+        <v>1500</v>
+      </c>
+      <c r="J4" s="4">
+        <v>900</v>
+      </c>
+      <c r="K4" s="4">
         <v>27</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E2" s="4" t="s">
+      <c r="L4" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="M4" s="4">
+        <v>2</v>
+      </c>
+      <c r="N4" s="4">
+        <v>1</v>
+      </c>
+      <c r="O4" s="4">
+        <v>10</v>
+      </c>
+      <c r="P4" s="4">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>1</v>
+      </c>
+      <c r="T4" s="5">
+        <v>1</v>
+      </c>
+      <c r="U4" s="5">
+        <v>1</v>
+      </c>
+      <c r="V4" s="5">
+        <v>1</v>
+      </c>
+      <c r="W4" s="5">
+        <v>1</v>
+      </c>
+      <c r="X4" s="5">
+        <v>1</v>
+      </c>
+      <c r="Y4" s="5">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="5">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="6">
         <v>30</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="O2" t="s">
-        <v>40</v>
-      </c>
-      <c r="P2" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q2" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="R2" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="S2" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="T2" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="U2" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="V2" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="W2" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="X2" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="Y2" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="Z2" s="6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1" spans="1:26">
-      <c r="A3" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="O3" t="s">
-        <v>58</v>
-      </c>
-      <c r="P3" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q3" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="R3" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="S3" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="T3" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="U3" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="V3" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="W3" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="X3" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y3" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z3" s="6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="4" ht="69" customHeight="1" spans="1:26">
-      <c r="A4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D4" s="4">
-        <v>80</v>
-      </c>
-      <c r="E4" s="4">
+      <c r="AB4" s="6">
         <v>30</v>
       </c>
-      <c r="F4" s="4">
-        <v>120</v>
-      </c>
-      <c r="G4" s="4">
-        <v>1500</v>
-      </c>
-      <c r="H4" s="4">
-        <v>900</v>
-      </c>
-      <c r="I4" s="4">
-        <v>27</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="K4" s="4">
-        <v>2</v>
-      </c>
-      <c r="L4" s="4">
-        <v>1</v>
-      </c>
-      <c r="M4" s="4">
-        <v>10</v>
-      </c>
-      <c r="N4" s="4">
-        <v>2</v>
-      </c>
-      <c r="P4" s="5">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="5">
-        <v>1</v>
-      </c>
-      <c r="R4" s="5">
-        <v>1</v>
-      </c>
-      <c r="S4" s="5">
-        <v>1</v>
-      </c>
-      <c r="T4" s="5">
-        <v>1</v>
-      </c>
-      <c r="U4" s="5">
-        <v>1</v>
-      </c>
-      <c r="V4" s="5">
-        <v>1</v>
-      </c>
-      <c r="W4" s="5">
-        <v>1</v>
-      </c>
-      <c r="X4" s="6">
-        <v>30</v>
-      </c>
-      <c r="Y4" s="6">
-        <v>30</v>
-      </c>
-      <c r="Z4" s="6">
+      <c r="AC4" s="6">
         <v>40</v>
       </c>
     </row>
     <row r="5" ht="69" customHeight="1"/>
     <row r="6" ht="69" customHeight="1"/>
-    <row r="7" ht="69" customHeight="1" spans="1:23">
+    <row r="7" ht="69" customHeight="1" spans="1:26">
       <c r="A7" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D7" s="4">
+        <v>71</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="4">
         <v>1000</v>
       </c>
-      <c r="E7" s="4">
+      <c r="F7" s="4">
         <v>0</v>
       </c>
-      <c r="I7" s="4">
+      <c r="G7" s="4">
+        <v>0</v>
+      </c>
+      <c r="K7" s="4">
         <v>30</v>
       </c>
-      <c r="N7" s="4">
-        <v>1</v>
-      </c>
-      <c r="P7" s="5">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="5">
-        <v>1</v>
-      </c>
-      <c r="R7" s="5">
-        <v>1</v>
+      <c r="P7" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="4" t="s">
+        <v>72</v>
       </c>
       <c r="S7" s="5">
         <v>1</v>
@@ -1617,61 +1691,70 @@
         <v>1</v>
       </c>
       <c r="W7" s="5">
+        <v>1</v>
+      </c>
+      <c r="X7" s="5">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="5">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="8" ht="69" customHeight="1"/>
-    <row r="9" ht="30" customHeight="1" spans="1:26">
+    <row r="9" ht="30" customHeight="1" spans="1:29">
       <c r="A9" s="4" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D9" s="4">
+        <v>74</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="4">
         <v>60</v>
       </c>
-      <c r="E9" s="4">
+      <c r="F9" s="4">
         <v>0</v>
       </c>
-      <c r="F9" s="4">
+      <c r="G9" s="4">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
         <v>20</v>
       </c>
-      <c r="G9" s="4">
+      <c r="I9" s="4">
         <v>1500</v>
       </c>
-      <c r="H9" s="4">
+      <c r="J9" s="4">
         <v>900</v>
       </c>
-      <c r="I9" s="4">
+      <c r="K9" s="4">
         <v>20</v>
       </c>
-      <c r="K9" s="4">
+      <c r="M9" s="4">
         <v>2</v>
       </c>
-      <c r="L9" s="4">
-        <v>1</v>
-      </c>
-      <c r="M9" s="4">
+      <c r="N9" s="4">
+        <v>1</v>
+      </c>
+      <c r="O9" s="4">
         <v>0</v>
       </c>
-      <c r="N9" s="4">
+      <c r="P9" s="4">
         <v>3</v>
       </c>
-      <c r="O9" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="P9" s="5">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="5">
-        <v>1</v>
-      </c>
-      <c r="R9" s="5">
-        <v>1</v>
+      <c r="Q9" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="R9" s="4" t="s">
+        <v>73</v>
       </c>
       <c r="S9" s="5">
         <v>1</v>
@@ -1688,64 +1771,73 @@
       <c r="W9" s="5">
         <v>1</v>
       </c>
-      <c r="X9" s="6">
+      <c r="X9" s="5">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="5">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="5">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="6">
         <v>30</v>
       </c>
-      <c r="Y9" s="6">
+      <c r="AB9" s="6">
         <v>30</v>
       </c>
-      <c r="Z9" s="6">
+      <c r="AC9" s="6">
         <v>30</v>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1" spans="2:23">
+    <row r="10" ht="34" customHeight="1" spans="2:26">
       <c r="B10" s="4" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D10" s="4">
+        <v>77</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="4">
         <v>50</v>
       </c>
-      <c r="E10" s="4">
+      <c r="F10" s="4">
         <v>0</v>
       </c>
-      <c r="F10" s="4">
+      <c r="G10" s="4">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
         <v>15</v>
       </c>
-      <c r="G10" s="4">
+      <c r="I10" s="4">
         <v>1500</v>
       </c>
-      <c r="H10" s="4">
+      <c r="J10" s="4">
         <v>900</v>
       </c>
-      <c r="I10" s="4">
+      <c r="K10" s="4">
         <v>20</v>
-      </c>
-      <c r="K10" s="4">
-        <v>0</v>
-      </c>
-      <c r="L10" s="4">
-        <v>0</v>
       </c>
       <c r="M10" s="4">
         <v>0</v>
       </c>
       <c r="N10" s="4">
+        <v>0</v>
+      </c>
+      <c r="O10" s="4">
+        <v>0</v>
+      </c>
+      <c r="P10" s="4">
         <v>3</v>
       </c>
-      <c r="O10" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="P10" s="5">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="5">
-        <v>1</v>
-      </c>
-      <c r="R10" s="5">
-        <v>1</v>
+      <c r="Q10" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="R10" s="4" t="s">
+        <v>76</v>
       </c>
       <c r="S10" s="5">
         <v>1</v>
@@ -1760,6 +1852,15 @@
         <v>1</v>
       </c>
       <c r="W10" s="5">
+        <v>1</v>
+      </c>
+      <c r="X10" s="5">
+        <v>1</v>
+      </c>
+      <c r="Y10" s="5">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="5">
         <v>1</v>
       </c>
     </row>
@@ -1777,24 +1878,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B2:B4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="3" outlineLevelCol="1"/>
   <cols>
     <col min="2" max="2" width="62.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="23.25" spans="2:2">
+    <row r="2" ht="26" spans="2:2">
       <c r="B2" s="1" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="3" ht="15" spans="2:2">
+    <row r="3" ht="17.6" spans="2:2">
       <c r="B3" s="2" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
     </row>
-    <row r="4" ht="15" spans="2:2">
+    <row r="4" ht="17.6" spans="2:2">
       <c r="B4" s="2" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -1808,7 +1909,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/GunfireDungeon_Godot/excel/RoleBase@角色属性.xlsx
+++ b/GunfireDungeon_Godot/excel/RoleBase@角色属性.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="18800"/>
+    <workbookView windowHeight="18780"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="79">
   <si>
     <t>Id</t>
   </si>
@@ -88,25 +88,22 @@
     <t>PhysicalResist</t>
   </si>
   <si>
-    <t>MagicResist</t>
-  </si>
-  <si>
     <t>FireResist</t>
   </si>
   <si>
-    <t>IceResist</t>
-  </si>
-  <si>
-    <t>ThunderResist</t>
-  </si>
-  <si>
-    <t>LightResist</t>
-  </si>
-  <si>
-    <t>DarkResist</t>
-  </si>
-  <si>
-    <t>RealResist</t>
+    <t>ElectricResist</t>
+  </si>
+  <si>
+    <t>ChemicalResist</t>
+  </si>
+  <si>
+    <t>OpticalResist</t>
+  </si>
+  <si>
+    <t>DarkMatterResist</t>
+  </si>
+  <si>
+    <t>ExplosiveResist</t>
   </si>
   <si>
     <t>AsBurningResist</t>
@@ -187,31 +184,25 @@
     <t>绑定的Ai属性</t>
   </si>
   <si>
-    <t>物理属性伤害抗性
-如果为1，也就是受到的伤害为100%。
-如果为0.5，就是受到的伤害为50%
-后面几个属性抗性意义相同</t>
-  </si>
-  <si>
-    <t>魔法属性伤害抗性</t>
-  </si>
-  <si>
-    <t>火焰属性伤害抗性</t>
-  </si>
-  <si>
-    <t>冰霜属性伤害抗性</t>
-  </si>
-  <si>
-    <t>雷电属性伤害抗性</t>
-  </si>
-  <si>
-    <t>光明属性伤害抗性</t>
-  </si>
-  <si>
-    <t>暗影属性伤害抗性</t>
-  </si>
-  <si>
-    <t>真实伤害属性伤害抗性，真实伤害指的是异常状态下受到的各种伤害，比如烧伤、中毒、出血等</t>
+    <t>物理减免</t>
+  </si>
+  <si>
+    <t>火焰减免</t>
+  </si>
+  <si>
+    <t>电击减免</t>
+  </si>
+  <si>
+    <t>化学减免</t>
+  </si>
+  <si>
+    <t>光学减免</t>
+  </si>
+  <si>
+    <t>暗物质减免</t>
+  </si>
+  <si>
+    <t>爆破减免</t>
   </si>
   <si>
     <t>燃烧异常状态抗性</t>
@@ -1267,7 +1258,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AC13"/>
+  <dimension ref="A1:AB13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="13.75" style="3" customWidth="1"/>
@@ -1289,13 +1280,12 @@
     <col min="22" max="22" width="17.75" style="5" customWidth="1"/>
     <col min="23" max="23" width="19.5" style="5" customWidth="1"/>
     <col min="24" max="24" width="16.5" style="5" customWidth="1"/>
-    <col min="25" max="25" width="15.5" style="5" customWidth="1"/>
-    <col min="26" max="26" width="16.125" style="5" customWidth="1"/>
-    <col min="27" max="27" width="21.5" style="6" customWidth="1"/>
-    <col min="28" max="29" width="27" style="6" customWidth="1"/>
+    <col min="25" max="25" width="18.2596153846154" style="5" customWidth="1"/>
+    <col min="26" max="26" width="21.5" style="6" customWidth="1"/>
+    <col min="27" max="28" width="27" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23" customHeight="1" spans="1:29">
+    <row r="1" ht="23" customHeight="1" spans="1:28">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1371,7 +1361,7 @@
       <c r="Y1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="5" t="s">
+      <c r="Z1" s="6" t="s">
         <v>25</v>
       </c>
       <c r="AA1" s="6" t="s">
@@ -1380,197 +1370,188 @@
       <c r="AB1" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="6" t="s">
+    </row>
+    <row r="2" ht="136" customHeight="1" spans="1:28">
+      <c r="A2" s="3" t="s">
         <v>28</v>
       </c>
+      <c r="B2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="R2" t="s">
+        <v>45</v>
+      </c>
+      <c r="S2" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="T2" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="U2" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="V2" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="W2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="X2" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y2" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z2" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA2" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AB2" s="6" t="s">
+        <v>55</v>
+      </c>
     </row>
-    <row r="2" ht="136" customHeight="1" spans="1:29">
-      <c r="A2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="R2" t="s">
-        <v>46</v>
-      </c>
-      <c r="S2" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="T2" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="U2" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="V2" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="W2" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="X2" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="Y2" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z2" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="AA2" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="AB2" s="6" t="s">
+    <row r="3" ht="30" customHeight="1" spans="1:28">
+      <c r="A3" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="AC2" s="6" t="s">
+      <c r="B3" s="4" t="s">
         <v>57</v>
       </c>
+      <c r="C3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="R3" t="s">
+        <v>64</v>
+      </c>
+      <c r="S3" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="T3" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="U3" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="V3" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="W3" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="X3" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y3" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z3" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="AA3" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="AB3" s="6" t="s">
+        <v>59</v>
+      </c>
     </row>
-    <row r="3" ht="30" customHeight="1" spans="1:29">
-      <c r="A3" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q3" s="4" t="s">
+    <row r="4" ht="69" customHeight="1" spans="1:28">
+      <c r="A4" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="R3" t="s">
+      <c r="B4" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>66</v>
-      </c>
-      <c r="S3" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="T3" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="U3" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="V3" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="W3" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="X3" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="Y3" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="Z3" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="AA3" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB3" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="AC3" s="6" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" ht="69" customHeight="1" spans="1:29">
-      <c r="A4" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>68</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>4</v>
@@ -1597,7 +1578,7 @@
         <v>27</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M4" s="4">
         <v>2</v>
@@ -1632,30 +1613,27 @@
       <c r="Y4" s="5">
         <v>1</v>
       </c>
-      <c r="Z4" s="5">
-        <v>1</v>
+      <c r="Z4" s="6">
+        <v>30</v>
       </c>
       <c r="AA4" s="6">
         <v>30</v>
       </c>
       <c r="AB4" s="6">
-        <v>30</v>
-      </c>
-      <c r="AC4" s="6">
         <v>40</v>
       </c>
     </row>
     <row r="5" ht="69" customHeight="1"/>
     <row r="6" ht="69" customHeight="1"/>
-    <row r="7" ht="69" customHeight="1" spans="1:26">
+    <row r="7" ht="69" customHeight="1" spans="1:25">
       <c r="A7" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>4</v>
@@ -1676,7 +1654,7 @@
         <v>1</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="S7" s="5">
         <v>1</v>
@@ -1697,22 +1675,19 @@
         <v>1</v>
       </c>
       <c r="Y7" s="5">
-        <v>1</v>
-      </c>
-      <c r="Z7" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="8" ht="69" customHeight="1"/>
-    <row r="9" ht="30" customHeight="1" spans="1:29">
+    <row r="9" ht="30" customHeight="1" spans="1:28">
       <c r="A9" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>4</v>
@@ -1751,10 +1726,10 @@
         <v>3</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="S9" s="5">
         <v>1</v>
@@ -1777,8 +1752,8 @@
       <c r="Y9" s="5">
         <v>1</v>
       </c>
-      <c r="Z9" s="5">
-        <v>1</v>
+      <c r="Z9" s="6">
+        <v>30</v>
       </c>
       <c r="AA9" s="6">
         <v>30</v>
@@ -1786,16 +1761,13 @@
       <c r="AB9" s="6">
         <v>30</v>
       </c>
-      <c r="AC9" s="6">
-        <v>30</v>
-      </c>
     </row>
-    <row r="10" ht="34" customHeight="1" spans="2:26">
+    <row r="10" ht="34" customHeight="1" spans="2:25">
       <c r="B10" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>4</v>
@@ -1834,10 +1806,10 @@
         <v>3</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="S10" s="5">
         <v>1</v>
@@ -1858,9 +1830,6 @@
         <v>1</v>
       </c>
       <c r="Y10" s="5">
-        <v>1</v>
-      </c>
-      <c r="Z10" s="5">
         <v>1</v>
       </c>
     </row>
@@ -1885,17 +1854,17 @@
   <sheetData>
     <row r="2" ht="26" spans="2:2">
       <c r="B2" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" ht="17.6" spans="2:2">
       <c r="B3" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" ht="17.6" spans="2:2">
       <c r="B4" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/GunfireDungeon_Godot/excel/RoleBase@角色属性.xlsx
+++ b/GunfireDungeon_Godot/excel/RoleBase@角色属性.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="18780"/>
+    <workbookView windowWidth="26480" windowHeight="15280"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="93">
   <si>
     <t>Id</t>
   </si>
@@ -46,10 +46,31 @@
     <t>Hp</t>
   </si>
   <si>
+    <t>Shield</t>
+  </si>
+  <si>
     <t>Armor</t>
   </si>
   <si>
-    <t>Shield</t>
+    <t>ShieldDelay</t>
+  </si>
+  <si>
+    <t>ShieldRate</t>
+  </si>
+  <si>
+    <t>ShieldInv</t>
+  </si>
+  <si>
+    <t>WoundInvPct</t>
+  </si>
+  <si>
+    <t>WoundInv</t>
+  </si>
+  <si>
+    <t>WoundMaxPct</t>
+  </si>
+  <si>
+    <t>WoundMaxInv</t>
   </si>
   <si>
     <t>MoveSpeed</t>
@@ -134,10 +155,31 @@
     <t>血量</t>
   </si>
   <si>
+    <t>护盾值</t>
+  </si>
+  <si>
     <t>装甲值</t>
   </si>
   <si>
-    <t>护盾值</t>
+    <t>护盾恢复延迟（秒）</t>
+  </si>
+  <si>
+    <t>护盾恢复速度，每秒恢复量，为0则不恢复</t>
+  </si>
+  <si>
+    <t>破盾后的无敌时间, 单位: 秒，为0则不触发无敌</t>
+  </si>
+  <si>
+    <t>每秒受到多少百分比伤害后触发无敌</t>
+  </si>
+  <si>
+    <t>受伤后的无敌时间, 单位: 秒，为0则不触发无敌</t>
+  </si>
+  <si>
+    <t>单次能受到最大的百分比伤害，也就是保护机制</t>
+  </si>
+  <si>
+    <t>触发保护机制后的无敌时间, 单位: 秒，为0则不触发无敌</t>
   </si>
   <si>
     <t>移动速度</t>
@@ -925,7 +967,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -940,6 +982,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1258,7 +1303,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AB13"/>
+  <dimension ref="A1:AI13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="13.75" style="3" customWidth="1"/>
@@ -1266,26 +1311,33 @@
     <col min="3" max="3" width="14" style="4" customWidth="1"/>
     <col min="4" max="4" width="23.0769230769231" style="4" customWidth="1"/>
     <col min="5" max="7" width="14" style="4" customWidth="1"/>
-    <col min="8" max="8" width="18.125" style="4" customWidth="1"/>
-    <col min="9" max="9" width="17" style="4" customWidth="1"/>
-    <col min="10" max="11" width="15" style="4" customWidth="1"/>
-    <col min="12" max="12" width="29.375" style="4" customWidth="1"/>
-    <col min="13" max="15" width="20.125" style="4" customWidth="1"/>
-    <col min="16" max="16" width="28.75" style="4" customWidth="1"/>
-    <col min="17" max="17" width="44.375" style="4" customWidth="1"/>
-    <col min="18" max="18" width="16.25" customWidth="1"/>
-    <col min="19" max="19" width="23.5480769230769" style="5" customWidth="1"/>
-    <col min="20" max="20" width="20.5096153846154" style="5" customWidth="1"/>
-    <col min="21" max="21" width="23.2307692307692" style="5" customWidth="1"/>
-    <col min="22" max="22" width="17.75" style="5" customWidth="1"/>
-    <col min="23" max="23" width="19.5" style="5" customWidth="1"/>
-    <col min="24" max="24" width="16.5" style="5" customWidth="1"/>
-    <col min="25" max="25" width="18.2596153846154" style="5" customWidth="1"/>
-    <col min="26" max="26" width="21.5" style="6" customWidth="1"/>
-    <col min="27" max="28" width="27" style="6" customWidth="1"/>
+    <col min="8" max="8" width="19.8653846153846" style="5" customWidth="1"/>
+    <col min="9" max="9" width="22.25" style="5" customWidth="1"/>
+    <col min="10" max="10" width="18.2692307692308" style="5" customWidth="1"/>
+    <col min="11" max="11" width="19.7307692307692" style="5" customWidth="1"/>
+    <col min="12" max="12" width="16.1538461538462" style="5" customWidth="1"/>
+    <col min="13" max="13" width="20.3846153846154" style="5" customWidth="1"/>
+    <col min="14" max="14" width="21.9903846153846" style="5" customWidth="1"/>
+    <col min="15" max="15" width="18.125" style="4" customWidth="1"/>
+    <col min="16" max="16" width="17" style="4" customWidth="1"/>
+    <col min="17" max="18" width="15" style="4" customWidth="1"/>
+    <col min="19" max="19" width="29.375" style="4" customWidth="1"/>
+    <col min="20" max="22" width="20.125" style="4" customWidth="1"/>
+    <col min="23" max="23" width="28.75" style="4" customWidth="1"/>
+    <col min="24" max="24" width="44.375" style="4" customWidth="1"/>
+    <col min="25" max="25" width="16.25" customWidth="1"/>
+    <col min="26" max="26" width="23.5480769230769" style="6" customWidth="1"/>
+    <col min="27" max="27" width="20.5096153846154" style="6" customWidth="1"/>
+    <col min="28" max="28" width="23.2307692307692" style="6" customWidth="1"/>
+    <col min="29" max="29" width="17.75" style="6" customWidth="1"/>
+    <col min="30" max="30" width="19.5" style="6" customWidth="1"/>
+    <col min="31" max="31" width="16.5" style="6" customWidth="1"/>
+    <col min="32" max="32" width="18.2596153846154" style="6" customWidth="1"/>
+    <col min="33" max="33" width="21.5" style="7" customWidth="1"/>
+    <col min="34" max="35" width="27" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23" customHeight="1" spans="1:28">
+    <row r="1" ht="23" customHeight="1" spans="1:35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1307,25 +1359,25 @@
       <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="5" t="s">
         <v>13</v>
       </c>
       <c r="O1" s="4" t="s">
@@ -1337,28 +1389,28 @@
       <c r="Q1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="S1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="T1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="U1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="V1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="5" t="s">
+      <c r="W1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="5" t="s">
+      <c r="X1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="5" t="s">
+      <c r="Y1" t="s">
         <v>24</v>
       </c>
       <c r="Z1" s="6" t="s">
@@ -1370,188 +1422,251 @@
       <c r="AB1" s="6" t="s">
         <v>27</v>
       </c>
+      <c r="AC1" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="7" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="2" ht="136" customHeight="1" spans="1:28">
+    <row r="2" ht="136" customHeight="1" spans="1:35">
       <c r="A2" s="3" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="N2" s="4" t="s">
         <v>41</v>
       </c>
+      <c r="H2" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>48</v>
+      </c>
       <c r="O2" s="4" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="R2" t="s">
-        <v>45</v>
-      </c>
-      <c r="S2" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="T2" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="U2" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="V2" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="W2" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="X2" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="Y2" s="5" t="s">
+      <c r="R2" s="4" t="s">
         <v>52</v>
       </c>
+      <c r="S2" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="X2" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>59</v>
+      </c>
       <c r="Z2" s="6" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="AA2" s="6" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="AB2" s="6" t="s">
-        <v>55</v>
+        <v>62</v>
+      </c>
+      <c r="AC2" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AD2" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="AE2" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AF2" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="AG2" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="AH2" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="AI2" s="7" t="s">
+        <v>69</v>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1" spans="1:28">
+    <row r="3" ht="30" customHeight="1" spans="1:35">
       <c r="A3" s="3" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>59</v>
+        <v>73</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>74</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="R3" t="s">
-        <v>64</v>
-      </c>
-      <c r="S3" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="T3" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="U3" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="V3" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="W3" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="X3" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="Y3" s="5" t="s">
-        <v>60</v>
+        <v>74</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="S3" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="T3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="U3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="V3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="W3" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="X3" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>78</v>
       </c>
       <c r="Z3" s="6" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="AA3" s="6" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="AB3" s="6" t="s">
-        <v>59</v>
+        <v>74</v>
+      </c>
+      <c r="AC3" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD3" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AE3" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AF3" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AG3" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="AH3" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI3" s="7" t="s">
+        <v>73</v>
       </c>
     </row>
-    <row r="4" ht="69" customHeight="1" spans="1:28">
+    <row r="4" ht="69" customHeight="1" spans="1:35">
       <c r="A4" s="4" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>4</v>
@@ -1560,80 +1675,101 @@
         <v>80</v>
       </c>
       <c r="F4" s="4">
+        <v>30</v>
+      </c>
+      <c r="G4" s="4">
         <v>0</v>
       </c>
-      <c r="G4" s="4">
+      <c r="H4" s="5">
+        <v>10</v>
+      </c>
+      <c r="I4" s="5">
+        <v>2</v>
+      </c>
+      <c r="J4" s="5">
+        <v>1.5</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="L4" s="5">
+        <v>1</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="N4" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="O4" s="4">
+        <v>120</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1500</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>900</v>
+      </c>
+      <c r="R4" s="4">
+        <v>27</v>
+      </c>
+      <c r="S4" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="T4" s="4">
+        <v>2</v>
+      </c>
+      <c r="U4" s="4">
+        <v>1</v>
+      </c>
+      <c r="V4" s="4">
+        <v>10</v>
+      </c>
+      <c r="W4" s="4">
+        <v>2</v>
+      </c>
+      <c r="Z4" s="6">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="6">
+        <v>1</v>
+      </c>
+      <c r="AB4" s="6">
+        <v>1</v>
+      </c>
+      <c r="AC4" s="6">
+        <v>1</v>
+      </c>
+      <c r="AD4" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE4" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF4" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG4" s="7">
         <v>30</v>
       </c>
-      <c r="H4" s="4">
-        <v>120</v>
-      </c>
-      <c r="I4" s="4">
-        <v>1500</v>
-      </c>
-      <c r="J4" s="4">
-        <v>900</v>
-      </c>
-      <c r="K4" s="4">
-        <v>27</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="M4" s="4">
-        <v>2</v>
-      </c>
-      <c r="N4" s="4">
-        <v>1</v>
-      </c>
-      <c r="O4" s="4">
-        <v>10</v>
-      </c>
-      <c r="P4" s="4">
-        <v>2</v>
-      </c>
-      <c r="S4" s="5">
-        <v>1</v>
-      </c>
-      <c r="T4" s="5">
-        <v>1</v>
-      </c>
-      <c r="U4" s="5">
-        <v>1</v>
-      </c>
-      <c r="V4" s="5">
-        <v>1</v>
-      </c>
-      <c r="W4" s="5">
-        <v>1</v>
-      </c>
-      <c r="X4" s="5">
-        <v>1</v>
-      </c>
-      <c r="Y4" s="5">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="6">
+      <c r="AH4" s="7">
         <v>30</v>
       </c>
-      <c r="AA4" s="6">
-        <v>30</v>
-      </c>
-      <c r="AB4" s="6">
+      <c r="AI4" s="7">
         <v>40</v>
       </c>
     </row>
     <row r="5" ht="69" customHeight="1"/>
     <row r="6" ht="69" customHeight="1"/>
-    <row r="7" ht="69" customHeight="1" spans="1:25">
+    <row r="7" ht="69" customHeight="1" spans="1:32">
       <c r="A7" s="4" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>4</v>
@@ -1647,47 +1783,47 @@
       <c r="G7" s="4">
         <v>0</v>
       </c>
-      <c r="K7" s="4">
+      <c r="R7" s="4">
         <v>30</v>
       </c>
-      <c r="P7" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="S7" s="5">
-        <v>1</v>
-      </c>
-      <c r="T7" s="5">
-        <v>1</v>
-      </c>
-      <c r="U7" s="5">
-        <v>1</v>
-      </c>
-      <c r="V7" s="5">
-        <v>1</v>
-      </c>
-      <c r="W7" s="5">
-        <v>1</v>
-      </c>
-      <c r="X7" s="5">
-        <v>1</v>
-      </c>
-      <c r="Y7" s="5">
+      <c r="W7" s="4">
+        <v>1</v>
+      </c>
+      <c r="X7" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z7" s="6">
+        <v>1</v>
+      </c>
+      <c r="AA7" s="6">
+        <v>1</v>
+      </c>
+      <c r="AB7" s="6">
+        <v>1</v>
+      </c>
+      <c r="AC7" s="6">
+        <v>1</v>
+      </c>
+      <c r="AD7" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE7" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF7" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="8" ht="69" customHeight="1"/>
-    <row r="9" ht="30" customHeight="1" spans="1:28">
+    <row r="9" ht="30" customHeight="1" spans="1:35">
       <c r="A9" s="4" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>4</v>
@@ -1701,73 +1837,73 @@
       <c r="G9" s="4">
         <v>0</v>
       </c>
-      <c r="H9" s="4">
+      <c r="O9" s="4">
         <v>20</v>
       </c>
-      <c r="I9" s="4">
+      <c r="P9" s="4">
         <v>1500</v>
       </c>
-      <c r="J9" s="4">
+      <c r="Q9" s="4">
         <v>900</v>
       </c>
-      <c r="K9" s="4">
+      <c r="R9" s="4">
         <v>20</v>
       </c>
-      <c r="M9" s="4">
+      <c r="T9" s="4">
         <v>2</v>
       </c>
-      <c r="N9" s="4">
-        <v>1</v>
-      </c>
-      <c r="O9" s="4">
+      <c r="U9" s="4">
+        <v>1</v>
+      </c>
+      <c r="V9" s="4">
         <v>0</v>
       </c>
-      <c r="P9" s="4">
+      <c r="W9" s="4">
         <v>3</v>
       </c>
-      <c r="Q9" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="R9" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="S9" s="5">
-        <v>1</v>
-      </c>
-      <c r="T9" s="5">
-        <v>1</v>
-      </c>
-      <c r="U9" s="5">
-        <v>1</v>
-      </c>
-      <c r="V9" s="5">
-        <v>1</v>
-      </c>
-      <c r="W9" s="5">
-        <v>1</v>
-      </c>
-      <c r="X9" s="5">
-        <v>1</v>
-      </c>
-      <c r="Y9" s="5">
-        <v>1</v>
+      <c r="X9" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y9" s="4" t="s">
+        <v>85</v>
       </c>
       <c r="Z9" s="6">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="6">
+        <v>1</v>
+      </c>
+      <c r="AB9" s="6">
+        <v>1</v>
+      </c>
+      <c r="AC9" s="6">
+        <v>1</v>
+      </c>
+      <c r="AD9" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE9" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF9" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG9" s="7">
         <v>30</v>
       </c>
-      <c r="AA9" s="6">
+      <c r="AH9" s="7">
         <v>30</v>
       </c>
-      <c r="AB9" s="6">
+      <c r="AI9" s="7">
         <v>30</v>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1" spans="2:25">
+    <row r="10" ht="34" customHeight="1" spans="2:32">
       <c r="B10" s="4" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>4</v>
@@ -1781,55 +1917,55 @@
       <c r="G10" s="4">
         <v>0</v>
       </c>
-      <c r="H10" s="4">
+      <c r="O10" s="4">
         <v>15</v>
       </c>
-      <c r="I10" s="4">
+      <c r="P10" s="4">
         <v>1500</v>
       </c>
-      <c r="J10" s="4">
+      <c r="Q10" s="4">
         <v>900</v>
       </c>
-      <c r="K10" s="4">
+      <c r="R10" s="4">
         <v>20</v>
       </c>
-      <c r="M10" s="4">
+      <c r="T10" s="4">
         <v>0</v>
       </c>
-      <c r="N10" s="4">
+      <c r="U10" s="4">
         <v>0</v>
       </c>
-      <c r="O10" s="4">
+      <c r="V10" s="4">
         <v>0</v>
       </c>
-      <c r="P10" s="4">
+      <c r="W10" s="4">
         <v>3</v>
       </c>
-      <c r="Q10" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="R10" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="S10" s="5">
-        <v>1</v>
-      </c>
-      <c r="T10" s="5">
-        <v>1</v>
-      </c>
-      <c r="U10" s="5">
-        <v>1</v>
-      </c>
-      <c r="V10" s="5">
-        <v>1</v>
-      </c>
-      <c r="W10" s="5">
-        <v>1</v>
-      </c>
-      <c r="X10" s="5">
-        <v>1</v>
-      </c>
-      <c r="Y10" s="5">
+      <c r="X10" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y10" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z10" s="6">
+        <v>1</v>
+      </c>
+      <c r="AA10" s="6">
+        <v>1</v>
+      </c>
+      <c r="AB10" s="6">
+        <v>1</v>
+      </c>
+      <c r="AC10" s="6">
+        <v>1</v>
+      </c>
+      <c r="AD10" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE10" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF10" s="6">
         <v>1</v>
       </c>
     </row>
@@ -1854,17 +1990,17 @@
   <sheetData>
     <row r="2" ht="26" spans="2:2">
       <c r="B2" s="1" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" ht="17.6" spans="2:2">
       <c r="B3" s="2" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" ht="17.6" spans="2:2">
       <c r="B4" s="2" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/GunfireDungeon_Godot/excel/RoleBase@角色属性.xlsx
+++ b/GunfireDungeon_Godot/excel/RoleBase@角色属性.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26480" windowHeight="15280"/>
+    <workbookView windowWidth="30500" windowHeight="17840"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/GunfireDungeon_Godot/excel/RoleBase@角色属性.xlsx
+++ b/GunfireDungeon_Godot/excel/RoleBase@角色属性.xlsx
@@ -1678,7 +1678,7 @@
         <v>30</v>
       </c>
       <c r="G4" s="4">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H4" s="5">
         <v>10</v>

--- a/GunfireDungeon_Godot/excel/RoleBase@角色属性.xlsx
+++ b/GunfireDungeon_Godot/excel/RoleBase@角色属性.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30500" windowHeight="17840"/>
+    <workbookView windowHeight="19180"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="107">
   <si>
     <t>Id</t>
   </si>
@@ -127,13 +127,34 @@
     <t>ExplosiveResist</t>
   </si>
   <si>
-    <t>AsBurningResist</t>
-  </si>
-  <si>
-    <t>AsPoisoningResist</t>
-  </si>
-  <si>
     <t>AsBleedingResist</t>
+  </si>
+  <si>
+    <t>AsIgniteResist</t>
+  </si>
+  <si>
+    <t>AsShortCircuitResist</t>
+  </si>
+  <si>
+    <t>AsInterferenceResist</t>
+  </si>
+  <si>
+    <t>AsElectricShockResist</t>
+  </si>
+  <si>
+    <t>AsCorrosionResist</t>
+  </si>
+  <si>
+    <t>AsFragileResist</t>
+  </si>
+  <si>
+    <t>AsBlindResist</t>
+  </si>
+  <si>
+    <t>AsChaosResist</t>
+  </si>
+  <si>
+    <t>AsArmorBreakResist</t>
   </si>
   <si>
     <t>表Id</t>
@@ -247,13 +268,34 @@
     <t>爆破减免</t>
   </si>
   <si>
-    <t>燃烧异常状态抗性</t>
-  </si>
-  <si>
-    <t>中毒异常状态抗性</t>
-  </si>
-  <si>
-    <t>出血异常状态抗性</t>
+    <t>流血异常状态抗性</t>
+  </si>
+  <si>
+    <t>点燃异常状态抗性</t>
+  </si>
+  <si>
+    <t>短路异常状态抗性</t>
+  </si>
+  <si>
+    <t>干扰异常状态抗性</t>
+  </si>
+  <si>
+    <t>触电异常状态抗性</t>
+  </si>
+  <si>
+    <t>腐蚀异常状态抗性</t>
+  </si>
+  <si>
+    <t>脆弱异常状态抗性</t>
+  </si>
+  <si>
+    <t>致盲异常状态抗性</t>
+  </si>
+  <si>
+    <t>混沌异常状态抗性</t>
+  </si>
+  <si>
+    <t>破甲异常状态抗性</t>
   </si>
   <si>
     <t>string</t>
@@ -1303,7 +1345,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AI13"/>
+  <dimension ref="A1:AP13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="13.75" style="3" customWidth="1"/>
@@ -1334,10 +1376,12 @@
     <col min="31" max="31" width="16.5" style="6" customWidth="1"/>
     <col min="32" max="32" width="18.2596153846154" style="6" customWidth="1"/>
     <col min="33" max="33" width="21.5" style="7" customWidth="1"/>
-    <col min="34" max="35" width="27" style="7" customWidth="1"/>
+    <col min="34" max="34" width="27" style="7" customWidth="1"/>
+    <col min="35" max="41" width="21.5" style="7" customWidth="1"/>
+    <col min="42" max="42" width="27" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23" customHeight="1" spans="1:35">
+    <row r="1" ht="23" customHeight="1" spans="1:42">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1443,230 +1487,293 @@
       <c r="AI1" s="7" t="s">
         <v>34</v>
       </c>
+      <c r="AJ1" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" s="7" t="s">
+        <v>41</v>
+      </c>
     </row>
-    <row r="2" ht="136" customHeight="1" spans="1:35">
+    <row r="2" ht="136" customHeight="1" spans="1:42">
       <c r="A2" s="3" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="V2" s="4" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="W2" s="4" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="X2" s="4" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="Y2" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="Z2" s="6" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="AA2" s="6" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="AB2" s="6" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="AC2" s="6" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="AD2" s="6" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="AE2" s="6" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="AF2" s="6" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="AG2" s="7" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="AH2" s="7" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="AI2" s="7" t="s">
-        <v>69</v>
+        <v>76</v>
+      </c>
+      <c r="AJ2" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="AK2" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="AL2" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AM2" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="AN2" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="AO2" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="AP2" s="7" t="s">
+        <v>83</v>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1" spans="1:35">
+    <row r="3" ht="30" customHeight="1" spans="1:42">
       <c r="A3" s="3" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="S3" s="4" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="U3" s="4" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="V3" s="4" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="W3" s="4" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="X3" s="4" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="Y3" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="Z3" s="6" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA3" s="6" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AB3" s="6" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AC3" s="6" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AD3" s="6" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AE3" s="6" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AF3" s="6" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AG3" s="7" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="AH3" s="7" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="AI3" s="7" t="s">
-        <v>73</v>
+        <v>87</v>
+      </c>
+      <c r="AJ3" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="AK3" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="AL3" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="AM3" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="AN3" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="AO3" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="AP3" s="7" t="s">
+        <v>87</v>
       </c>
     </row>
-    <row r="4" ht="69" customHeight="1" spans="1:35">
+    <row r="4" ht="69" customHeight="1" spans="1:42">
       <c r="A4" s="4" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>4</v>
@@ -1714,7 +1821,7 @@
         <v>27</v>
       </c>
       <c r="S4" s="4" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="T4" s="4">
         <v>2</v>
@@ -1757,19 +1864,40 @@
       </c>
       <c r="AI4" s="7">
         <v>40</v>
+      </c>
+      <c r="AJ4" s="7">
+        <v>30</v>
+      </c>
+      <c r="AK4" s="7">
+        <v>30</v>
+      </c>
+      <c r="AL4" s="7">
+        <v>30</v>
+      </c>
+      <c r="AM4" s="7">
+        <v>30</v>
+      </c>
+      <c r="AN4" s="7">
+        <v>30</v>
+      </c>
+      <c r="AO4" s="7">
+        <v>30</v>
+      </c>
+      <c r="AP4" s="7">
+        <v>30</v>
       </c>
     </row>
     <row r="5" ht="69" customHeight="1"/>
     <row r="6" ht="69" customHeight="1"/>
     <row r="7" ht="69" customHeight="1" spans="1:32">
       <c r="A7" s="4" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>4</v>
@@ -1790,7 +1918,7 @@
         <v>1</v>
       </c>
       <c r="X7" s="4" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="Z7" s="6">
         <v>1</v>
@@ -1815,15 +1943,15 @@
       </c>
     </row>
     <row r="8" ht="69" customHeight="1"/>
-    <row r="9" ht="30" customHeight="1" spans="1:35">
+    <row r="9" ht="30" customHeight="1" spans="1:42">
       <c r="A9" s="4" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>4</v>
@@ -1862,10 +1990,10 @@
         <v>3</v>
       </c>
       <c r="X9" s="4" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="Y9" s="4" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="Z9" s="6">
         <v>1</v>
@@ -1895,15 +2023,36 @@
         <v>30</v>
       </c>
       <c r="AI9" s="7">
+        <v>30</v>
+      </c>
+      <c r="AJ9" s="7">
+        <v>30</v>
+      </c>
+      <c r="AK9" s="7">
+        <v>30</v>
+      </c>
+      <c r="AL9" s="7">
+        <v>30</v>
+      </c>
+      <c r="AM9" s="7">
+        <v>30</v>
+      </c>
+      <c r="AN9" s="7">
+        <v>30</v>
+      </c>
+      <c r="AO9" s="7">
+        <v>30</v>
+      </c>
+      <c r="AP9" s="7">
         <v>30</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="2:32">
       <c r="B10" s="4" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>4</v>
@@ -1942,10 +2091,10 @@
         <v>3</v>
       </c>
       <c r="X10" s="4" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="Y10" s="4" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="Z10" s="6">
         <v>1</v>
@@ -1990,17 +2139,17 @@
   <sheetData>
     <row r="2" ht="26" spans="2:2">
       <c r="B2" s="1" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" ht="17.6" spans="2:2">
       <c r="B3" s="2" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" ht="17.6" spans="2:2">
       <c r="B4" s="2" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/GunfireDungeon_Godot/excel/RoleBase@角色属性.xlsx
+++ b/GunfireDungeon_Godot/excel/RoleBase@角色属性.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="109">
   <si>
     <t>Id</t>
   </si>
@@ -104,6 +104,9 @@
   </si>
   <si>
     <t>AiAttr</t>
+  </si>
+  <si>
+    <t>CritResist</t>
   </si>
   <si>
     <t>PhysicalResist</t>
@@ -245,6 +248,9 @@
   </si>
   <si>
     <t>绑定的Ai属性</t>
+  </si>
+  <si>
+    <t>抗暴击率</t>
   </si>
   <si>
     <t>物理减免</t>
@@ -1009,7 +1015,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1027,6 +1033,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1345,7 +1354,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AP13"/>
+  <dimension ref="A1:AQ13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="13.75" style="3" customWidth="1"/>
@@ -1368,20 +1377,21 @@
     <col min="23" max="23" width="28.75" style="4" customWidth="1"/>
     <col min="24" max="24" width="44.375" style="4" customWidth="1"/>
     <col min="25" max="25" width="16.25" customWidth="1"/>
-    <col min="26" max="26" width="23.5480769230769" style="6" customWidth="1"/>
-    <col min="27" max="27" width="20.5096153846154" style="6" customWidth="1"/>
-    <col min="28" max="28" width="23.2307692307692" style="6" customWidth="1"/>
-    <col min="29" max="29" width="17.75" style="6" customWidth="1"/>
-    <col min="30" max="30" width="19.5" style="6" customWidth="1"/>
-    <col min="31" max="31" width="16.5" style="6" customWidth="1"/>
-    <col min="32" max="32" width="18.2596153846154" style="6" customWidth="1"/>
-    <col min="33" max="33" width="21.5" style="7" customWidth="1"/>
-    <col min="34" max="34" width="27" style="7" customWidth="1"/>
-    <col min="35" max="41" width="21.5" style="7" customWidth="1"/>
-    <col min="42" max="42" width="27" style="7" customWidth="1"/>
+    <col min="26" max="26" width="16.25" style="6" customWidth="1"/>
+    <col min="27" max="27" width="23.5480769230769" style="7" customWidth="1"/>
+    <col min="28" max="28" width="20.5096153846154" style="7" customWidth="1"/>
+    <col min="29" max="29" width="23.2307692307692" style="7" customWidth="1"/>
+    <col min="30" max="30" width="17.75" style="7" customWidth="1"/>
+    <col min="31" max="31" width="19.5" style="7" customWidth="1"/>
+    <col min="32" max="32" width="16.5" style="7" customWidth="1"/>
+    <col min="33" max="33" width="18.2596153846154" style="7" customWidth="1"/>
+    <col min="34" max="34" width="21.5" style="8" customWidth="1"/>
+    <col min="35" max="35" width="27" style="8" customWidth="1"/>
+    <col min="36" max="42" width="21.5" style="8" customWidth="1"/>
+    <col min="43" max="43" width="27" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23" customHeight="1" spans="1:42">
+    <row r="1" ht="23" customHeight="1" spans="1:43">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1460,320 +1470,329 @@
       <c r="Z1" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="6" t="s">
+      <c r="AA1" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="6" t="s">
+      <c r="AB1" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="6" t="s">
+      <c r="AC1" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="6" t="s">
+      <c r="AD1" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="6" t="s">
+      <c r="AE1" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="6" t="s">
+      <c r="AF1" s="7" t="s">
         <v>31</v>
       </c>
       <c r="AG1" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="7" t="s">
+      <c r="AH1" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="7" t="s">
+      <c r="AI1" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="7" t="s">
+      <c r="AJ1" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="7" t="s">
+      <c r="AK1" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="7" t="s">
+      <c r="AL1" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="7" t="s">
+      <c r="AM1" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="7" t="s">
+      <c r="AN1" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="7" t="s">
+      <c r="AO1" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="7" t="s">
+      <c r="AP1" s="8" t="s">
         <v>41</v>
       </c>
+      <c r="AQ1" s="8" t="s">
+        <v>42</v>
+      </c>
     </row>
-    <row r="2" ht="136" customHeight="1" spans="1:42">
+    <row r="2" ht="136" customHeight="1" spans="1:43">
       <c r="A2" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="V2" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="W2" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="X2" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Y2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Z2" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA2" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="AB2" s="6" t="s">
+      <c r="AA2" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="AC2" s="6" t="s">
+      <c r="AB2" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="AD2" s="6" t="s">
+      <c r="AC2" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="AE2" s="6" t="s">
+      <c r="AD2" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="AF2" s="6" t="s">
+      <c r="AE2" s="7" t="s">
         <v>73</v>
       </c>
+      <c r="AF2" s="7" t="s">
+        <v>74</v>
+      </c>
       <c r="AG2" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="AH2" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="AI2" s="7" t="s">
+      <c r="AH2" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="AJ2" s="7" t="s">
+      <c r="AI2" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="AK2" s="7" t="s">
+      <c r="AJ2" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="AL2" s="7" t="s">
+      <c r="AK2" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="AM2" s="7" t="s">
+      <c r="AL2" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="AN2" s="7" t="s">
+      <c r="AM2" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="AO2" s="7" t="s">
+      <c r="AN2" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="AP2" s="7" t="s">
+      <c r="AO2" s="8" t="s">
         <v>83</v>
       </c>
+      <c r="AP2" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="AQ2" s="8" t="s">
+        <v>85</v>
+      </c>
     </row>
-    <row r="3" ht="30" customHeight="1" spans="1:42">
+    <row r="3" ht="30" customHeight="1" spans="1:43">
       <c r="A3" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="S3" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="T3" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="T3" s="4" t="s">
-        <v>87</v>
-      </c>
       <c r="U3" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="V3" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="W3" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="X3" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>94</v>
+      </c>
+      <c r="Z3" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="X3" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z3" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="AA3" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="AB3" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="AC3" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="AD3" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="AE3" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="AF3" s="6" t="s">
-        <v>88</v>
+      <c r="AA3" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="AB3" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC3" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="AD3" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE3" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="AF3" s="7" t="s">
+        <v>90</v>
       </c>
       <c r="AG3" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="AH3" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="AI3" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="AJ3" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="AK3" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="AL3" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="AM3" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="AN3" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="AO3" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="AP3" s="7" t="s">
-        <v>87</v>
+        <v>90</v>
+      </c>
+      <c r="AH3" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI3" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="AJ3" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="AK3" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="AL3" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="AM3" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="AN3" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="AO3" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="AP3" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="AQ3" s="8" t="s">
+        <v>89</v>
       </c>
     </row>
-    <row r="4" ht="69" customHeight="1" spans="1:42">
+    <row r="4" ht="69" customHeight="1" spans="1:43">
       <c r="A4" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>4</v>
@@ -1821,7 +1840,7 @@
         <v>27</v>
       </c>
       <c r="S4" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="T4" s="4">
         <v>2</v>
@@ -1836,68 +1855,71 @@
         <v>2</v>
       </c>
       <c r="Z4" s="6">
-        <v>1</v>
-      </c>
-      <c r="AA4" s="6">
-        <v>1</v>
-      </c>
-      <c r="AB4" s="6">
-        <v>1</v>
-      </c>
-      <c r="AC4" s="6">
-        <v>1</v>
-      </c>
-      <c r="AD4" s="6">
-        <v>1</v>
-      </c>
-      <c r="AE4" s="6">
-        <v>1</v>
-      </c>
-      <c r="AF4" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="AA4" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB4" s="7">
+        <v>1</v>
+      </c>
+      <c r="AC4" s="7">
+        <v>1</v>
+      </c>
+      <c r="AD4" s="7">
+        <v>1</v>
+      </c>
+      <c r="AE4" s="7">
+        <v>1</v>
+      </c>
+      <c r="AF4" s="7">
         <v>1</v>
       </c>
       <c r="AG4" s="7">
+        <v>1</v>
+      </c>
+      <c r="AH4" s="8">
         <v>30</v>
       </c>
-      <c r="AH4" s="7">
+      <c r="AI4" s="8">
         <v>30</v>
       </c>
-      <c r="AI4" s="7">
+      <c r="AJ4" s="8">
         <v>40</v>
       </c>
-      <c r="AJ4" s="7">
+      <c r="AK4" s="8">
         <v>30</v>
       </c>
-      <c r="AK4" s="7">
+      <c r="AL4" s="8">
         <v>30</v>
       </c>
-      <c r="AL4" s="7">
+      <c r="AM4" s="8">
         <v>30</v>
       </c>
-      <c r="AM4" s="7">
+      <c r="AN4" s="8">
         <v>30</v>
       </c>
-      <c r="AN4" s="7">
+      <c r="AO4" s="8">
         <v>30</v>
       </c>
-      <c r="AO4" s="7">
+      <c r="AP4" s="8">
         <v>30</v>
       </c>
-      <c r="AP4" s="7">
+      <c r="AQ4" s="8">
         <v>30</v>
       </c>
     </row>
     <row r="5" ht="69" customHeight="1"/>
     <row r="6" ht="69" customHeight="1"/>
-    <row r="7" ht="69" customHeight="1" spans="1:32">
+    <row r="7" ht="69" customHeight="1" spans="1:33">
       <c r="A7" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>4</v>
@@ -1918,40 +1940,40 @@
         <v>1</v>
       </c>
       <c r="X7" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="Z7" s="6">
-        <v>1</v>
-      </c>
-      <c r="AA7" s="6">
-        <v>1</v>
-      </c>
-      <c r="AB7" s="6">
-        <v>1</v>
-      </c>
-      <c r="AC7" s="6">
-        <v>1</v>
-      </c>
-      <c r="AD7" s="6">
-        <v>1</v>
-      </c>
-      <c r="AE7" s="6">
-        <v>1</v>
-      </c>
-      <c r="AF7" s="6">
+        <v>100</v>
+      </c>
+      <c r="AA7" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB7" s="7">
+        <v>1</v>
+      </c>
+      <c r="AC7" s="7">
+        <v>1</v>
+      </c>
+      <c r="AD7" s="7">
+        <v>1</v>
+      </c>
+      <c r="AE7" s="7">
+        <v>1</v>
+      </c>
+      <c r="AF7" s="7">
+        <v>1</v>
+      </c>
+      <c r="AG7" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="8" ht="69" customHeight="1"/>
-    <row r="9" ht="30" customHeight="1" spans="1:42">
+    <row r="9" ht="30" customHeight="1" spans="1:43">
       <c r="A9" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>4</v>
@@ -1990,69 +2012,72 @@
         <v>3</v>
       </c>
       <c r="X9" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="Y9" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="Y9" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="Z9" s="6">
-        <v>1</v>
-      </c>
-      <c r="AA9" s="6">
-        <v>1</v>
-      </c>
-      <c r="AB9" s="6">
-        <v>1</v>
-      </c>
-      <c r="AC9" s="6">
-        <v>1</v>
-      </c>
-      <c r="AD9" s="6">
-        <v>1</v>
-      </c>
-      <c r="AE9" s="6">
-        <v>1</v>
-      </c>
-      <c r="AF9" s="6">
+      <c r="Z9" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB9" s="7">
+        <v>1</v>
+      </c>
+      <c r="AC9" s="7">
+        <v>1</v>
+      </c>
+      <c r="AD9" s="7">
+        <v>1</v>
+      </c>
+      <c r="AE9" s="7">
+        <v>1</v>
+      </c>
+      <c r="AF9" s="7">
         <v>1</v>
       </c>
       <c r="AG9" s="7">
+        <v>1</v>
+      </c>
+      <c r="AH9" s="8">
         <v>30</v>
       </c>
-      <c r="AH9" s="7">
+      <c r="AI9" s="8">
         <v>30</v>
       </c>
-      <c r="AI9" s="7">
+      <c r="AJ9" s="8">
         <v>30</v>
       </c>
-      <c r="AJ9" s="7">
+      <c r="AK9" s="8">
         <v>30</v>
       </c>
-      <c r="AK9" s="7">
+      <c r="AL9" s="8">
         <v>30</v>
       </c>
-      <c r="AL9" s="7">
+      <c r="AM9" s="8">
         <v>30</v>
       </c>
-      <c r="AM9" s="7">
+      <c r="AN9" s="8">
         <v>30</v>
       </c>
-      <c r="AN9" s="7">
+      <c r="AO9" s="8">
         <v>30</v>
       </c>
-      <c r="AO9" s="7">
+      <c r="AP9" s="8">
         <v>30</v>
       </c>
-      <c r="AP9" s="7">
+      <c r="AQ9" s="8">
         <v>30</v>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1" spans="2:32">
+    <row r="10" ht="34" customHeight="1" spans="2:33">
       <c r="B10" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>4</v>
@@ -2091,30 +2116,33 @@
         <v>3</v>
       </c>
       <c r="X10" s="4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="Y10" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="Z10" s="6">
-        <v>1</v>
-      </c>
-      <c r="AA10" s="6">
-        <v>1</v>
-      </c>
-      <c r="AB10" s="6">
-        <v>1</v>
-      </c>
-      <c r="AC10" s="6">
-        <v>1</v>
-      </c>
-      <c r="AD10" s="6">
-        <v>1</v>
-      </c>
-      <c r="AE10" s="6">
-        <v>1</v>
-      </c>
-      <c r="AF10" s="6">
+        <v>104</v>
+      </c>
+      <c r="Z10" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB10" s="7">
+        <v>1</v>
+      </c>
+      <c r="AC10" s="7">
+        <v>1</v>
+      </c>
+      <c r="AD10" s="7">
+        <v>1</v>
+      </c>
+      <c r="AE10" s="7">
+        <v>1</v>
+      </c>
+      <c r="AF10" s="7">
+        <v>1</v>
+      </c>
+      <c r="AG10" s="7">
         <v>1</v>
       </c>
     </row>
@@ -2139,17 +2167,17 @@
   <sheetData>
     <row r="2" ht="26" spans="2:2">
       <c r="B2" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" ht="17.6" spans="2:2">
       <c r="B3" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" ht="17.6" spans="2:2">
       <c r="B4" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/GunfireDungeon_Godot/excel/RoleBase@角色属性.xlsx
+++ b/GunfireDungeon_Godot/excel/RoleBase@角色属性.xlsx
@@ -109,25 +109,25 @@
     <t>CritResist</t>
   </si>
   <si>
-    <t>PhysicalResist</t>
-  </si>
-  <si>
-    <t>FireResist</t>
-  </si>
-  <si>
-    <t>ElectricResist</t>
-  </si>
-  <si>
-    <t>ChemicalResist</t>
-  </si>
-  <si>
-    <t>OpticalResist</t>
-  </si>
-  <si>
-    <t>DarkMatterResist</t>
-  </si>
-  <si>
-    <t>ExplosiveResist</t>
+    <t>PhysicalReduce</t>
+  </si>
+  <si>
+    <t>FireReduce</t>
+  </si>
+  <si>
+    <t>ElectricReduce</t>
+  </si>
+  <si>
+    <t>ChemicalReduce</t>
+  </si>
+  <si>
+    <t>OpticalReduce</t>
+  </si>
+  <si>
+    <t>DarkMatterReduce</t>
+  </si>
+  <si>
+    <t>ExplosiveReduce</t>
   </si>
   <si>
     <t>AsBleedingResist</t>
@@ -1383,7 +1383,7 @@
     <col min="29" max="29" width="23.2307692307692" style="7" customWidth="1"/>
     <col min="30" max="30" width="17.75" style="7" customWidth="1"/>
     <col min="31" max="31" width="19.5" style="7" customWidth="1"/>
-    <col min="32" max="32" width="16.5" style="7" customWidth="1"/>
+    <col min="32" max="32" width="18.9326923076923" style="7" customWidth="1"/>
     <col min="33" max="33" width="18.2596153846154" style="7" customWidth="1"/>
     <col min="34" max="34" width="21.5" style="8" customWidth="1"/>
     <col min="35" max="35" width="27" style="8" customWidth="1"/>
@@ -1858,25 +1858,25 @@
         <v>0.1</v>
       </c>
       <c r="AA4" s="7">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="AB4" s="7">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="AC4" s="7">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="AD4" s="7">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="AE4" s="7">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="AF4" s="7">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="AG4" s="7">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="AH4" s="8">
         <v>30</v>
@@ -1943,25 +1943,25 @@
         <v>100</v>
       </c>
       <c r="AA7" s="7">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="AB7" s="7">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="AC7" s="7">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="AD7" s="7">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="AE7" s="7">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="AF7" s="7">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="AG7" s="7">
-        <v>1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="8" ht="69" customHeight="1"/>
@@ -2021,25 +2021,25 @@
         <v>0</v>
       </c>
       <c r="AA9" s="7">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="AB9" s="7">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="AC9" s="7">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="AD9" s="7">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="AE9" s="7">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="AF9" s="7">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="AG9" s="7">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="AH9" s="8">
         <v>30</v>
@@ -2125,25 +2125,25 @@
         <v>0</v>
       </c>
       <c r="AA10" s="7">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="AB10" s="7">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="AC10" s="7">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="AD10" s="7">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="AE10" s="7">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="AF10" s="7">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="AG10" s="7">
-        <v>1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1"/>
